--- a/case_studies/backbone_2026/technologies.xlsx
+++ b/case_studies/backbone_2026/technologies.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\AdOpT-NET0_my\case_studies\backbone_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3EE2A15-8EDF-4AB0-B1ED-CFBE44A8D17C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16B7F995-16AD-4DF2-925D-4F55DD5167F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="existing" sheetId="3" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="33">
   <si>
     <t>cluster</t>
   </si>
@@ -134,6 +134,9 @@
   </si>
   <si>
     <t>PEMEC</t>
+  </si>
+  <si>
+    <t>CO2toEmissions</t>
   </si>
 </sst>
 </file>
@@ -451,10 +454,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A32646D9-68BB-474D-B725-BABE5F54D2FA}">
-  <dimension ref="A1:Y8"/>
+  <dimension ref="A1:Z8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -530,8 +533,11 @@
       <c r="Y1" t="s">
         <v>29</v>
       </c>
+      <c r="Z1" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -607,8 +613,11 @@
       <c r="Y2">
         <v>0</v>
       </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -684,8 +693,11 @@
       <c r="Y3">
         <v>0</v>
       </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -761,8 +773,11 @@
       <c r="Y4">
         <v>0</v>
       </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -838,8 +853,11 @@
       <c r="Y5">
         <v>0</v>
       </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -915,8 +933,11 @@
       <c r="Y6">
         <v>0</v>
       </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -992,8 +1013,11 @@
       <c r="Y7">
         <v>0</v>
       </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -1067,6 +1091,9 @@
         <v>0</v>
       </c>
       <c r="Y8">
+        <v>0</v>
+      </c>
+      <c r="Z8">
         <v>0</v>
       </c>
     </row>
@@ -1077,10 +1104,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B7B1BB4-9645-4A08-BE86-AFBC7A2F79A5}">
-  <dimension ref="A1:Y8"/>
+  <dimension ref="A1:Z8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1156,8 +1183,11 @@
       <c r="Y1" t="s">
         <v>29</v>
       </c>
+      <c r="Z1" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -1234,7 +1264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1311,7 +1341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1388,7 +1418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -1465,7 +1495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -1542,7 +1572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -1619,7 +1649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -1703,10 +1733,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD6448D7-10EE-4973-BCA6-F7E0B963E195}">
-  <dimension ref="A1:Y8"/>
+  <dimension ref="A1:Z8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1782,8 +1812,11 @@
       <c r="Y1" t="s">
         <v>29</v>
       </c>
+      <c r="Z1" t="s">
+        <v>32</v>
+      </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -1859,8 +1892,11 @@
       <c r="Y2">
         <v>0</v>
       </c>
+      <c r="Z2">
+        <v>1</v>
+      </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1936,8 +1972,11 @@
       <c r="Y3">
         <v>0</v>
       </c>
+      <c r="Z3">
+        <v>1</v>
+      </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -2013,8 +2052,11 @@
       <c r="Y4">
         <v>0</v>
       </c>
+      <c r="Z4">
+        <v>1</v>
+      </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -2090,8 +2132,11 @@
       <c r="Y5">
         <v>0</v>
       </c>
+      <c r="Z5">
+        <v>1</v>
+      </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -2167,8 +2212,11 @@
       <c r="Y6">
         <v>0</v>
       </c>
+      <c r="Z6">
+        <v>1</v>
+      </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -2244,8 +2292,11 @@
       <c r="Y7">
         <v>0</v>
       </c>
+      <c r="Z7">
+        <v>1</v>
+      </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -2320,6 +2371,9 @@
       </c>
       <c r="Y8">
         <v>0</v>
+      </c>
+      <c r="Z8">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
